--- a/roteiros/roteiro-videos-treinos.xlsx
+++ b/roteiros/roteiro-videos-treinos.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="721">
   <si>
     <t xml:space="preserve">Avante IA — Roteiro dos vídeos de treino (acervo completo do app)</t>
   </si>
@@ -100,7 +100,7 @@
     <t xml:space="preserve">Lateral</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a dumbbell squat into calf raise: holding a dumbbell in each hand, performs a full squat, stands up fully and rises onto the balls of the feet, then lowers the heels. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: dumbbell squat into calf raise: holding a dumbbell in each hand, performs a full squat, stands up fully and rises onto the balls of the feet, then lowers the heels. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">agacho_pausa</t>
@@ -121,7 +121,7 @@
     <t xml:space="preserve">Desça controlando, fique 3 segundos parada(o) lá embaixo e suba firme.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pause squat: lowers with control, holds three seconds at the bottom, then stands up firmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: pause squat: lowers with control, holds three seconds at the bottom, then stands up firmly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">agacho_salto</t>
@@ -145,7 +145,7 @@
     <t xml:space="preserve">Frontal 45°</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a jump squat: squats and explodes upward, lands softly and goes straight into the next squat. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: jump squat: squats and explodes upward, lands softly and goes straight into the next squat. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">agacho_split</t>
@@ -163,7 +163,7 @@
     <t xml:space="preserve">Lateral 45°</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a split squat: one foot forward and one back, feet fixed, lowers straight down until the back knee nearly touches the floor, then rises. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: split squat: one foot forward and one back, feet fixed, lowers straight down until the back knee nearly touches the floor, then rises. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">agacho_goblet</t>
@@ -181,7 +181,7 @@
     <t xml:space="preserve">Segure o peso junto ao peito, cotovelos apontando pra baixo, desça com o tronco ereto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a goblet squat: holds one dumbbell vertically against the chest with elbows pointing down, squats deep with an upright torso and stands up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: goblet squat: holds one dumbbell vertically against the chest with elbows pointing down, squats deep with an upright torso and stands up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">agacho_iso</t>
@@ -196,7 +196,7 @@
     <t xml:space="preserve">Costas na parede, joelhos a 90°, segure a posição respirando.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs a steady wall sit: back flat against a wall, knees at 90 degrees, holding the position. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: wall sit: back flat against a wall, knees at 90 degrees, holding the position. The person holds the position still for the whole clip, breathing calmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">agacho</t>
@@ -208,7 +208,7 @@
     <t xml:space="preserve">Pés na largura do quadril, desça como quem senta numa cadeira, joelhos alinhados com os pés.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a bodyweight squat: feet hip-width apart, sits the hips back and down as if onto a chair until thighs are parallel, knees tracking over toes, then stands up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: bodyweight squat: feet hip-width apart, sits the hips back and down as if onto a chair until thighs are parallel, knees tracking over toes, then stands up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">sumo</t>
@@ -223,7 +223,7 @@
     <t xml:space="preserve">Frontal</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a bodyweight sumo squat: very wide stance with toes pointed out, upright torso, lowers with control and stands back up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: bodyweight sumo squat: very wide stance with toes pointed out, upright torso, lowers with control and stands back up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">sumo_remada</t>
@@ -238,7 +238,7 @@
     <t xml:space="preserve">No topo do sumô, puxe o peso até a altura do queixo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a sumo squat to upright row: wide stance, one dumbbell held with both hands, squats down and on the way up pulls the dumbbell to chin height with elbows high. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: sumo squat to upright row: wide stance, one dumbbell held with both hands, squats down and on the way up pulls the dumbbell to chin height with elbows high. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">pant_uni</t>
@@ -256,7 +256,7 @@
     <t xml:space="preserve">Na beirada de um degrau, suba na ponta do pé devagar e desça até alongar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-leg calf raise: on the edge of a step, rises slowly onto the toes of one foot and lowers into a stretch. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: single-leg calf raise: on the edge of a step, rises slowly onto the toes of one foot and lowers into a stretch. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">iso_ponta</t>
@@ -268,7 +268,7 @@
     <t xml:space="preserve">Fique na ponta dos pés com os joelhos levemente dobrados e segure firme.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs a steady isometric calf hold: standing on the balls of the feet with knees slightly bent, holding firm. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: isometric calf hold: standing on the balls of the feet with knees slightly bent, holding firm. The person holds the position still for the whole clip, breathing calmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">pant_degrau</t>
@@ -283,7 +283,7 @@
     <t xml:space="preserve">Pontas dos pés no degrau, suba o máximo que der e desça alongando.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a standing calf raise on a step: balls of the feet on a step, rises as high as possible and lowers into a stretch. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: standing calf raise on a step: balls of the feet on a step, rises as high as possible and lowers into a stretch. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">pe_toalha</t>
@@ -301,7 +301,10 @@
     <t xml:space="preserve">Sentada(o), pé em cima de uma toalha no chão: puxe a toalha pra perto usando só os dedos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs a continuous towel scrunches: seated, one foot on a towel on the floor, pulls the towel closer using only the toes. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Lateral (close nos pés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: low side view, close-up on the feet and lower legs, steady shot, natural lighting. Exercise: close-up of a bare foot on a small towel on the floor, the toes scrunch and pull the towel toward the foot. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">swing</t>
@@ -319,7 +322,7 @@
     <t xml:space="preserve">O quadril impulsiona o peso até a altura do ombro, com os braços relaxados.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a kettlebell swing: hinges and swings the kettlebell between the legs, then snaps the hips forward so the bell floats to shoulder height with relaxed arms. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: kettlebell swing: hinges and swings the kettlebell between the legs, then snaps the hips forward so the bell floats to shoulder height with relaxed arms. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">bom_dia_pausa</t>
@@ -334,7 +337,7 @@
     <t xml:space="preserve">Leve o quadril pra trás com as costas retas, pare 2 segundos embaixo e suba apertando o glúteo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pause good morning: hands behind the head, hinges the hips back with a flat back, pauses two seconds at the bottom, stands up squeezing the glutes. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: standing hip hinge with hands behind the head: pushes the hips back with a flat back, pauses two seconds at the bottom, then stands up squeezing the glutes. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">bom_dia</t>
@@ -346,7 +349,7 @@
     <t xml:space="preserve">Mãos atrás da cabeça, joelhos levemente dobrados, leve o quadril pra trás com as costas retas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a bodyweight good morning: hands behind the head, knees slightly bent, hinges the hips back with a flat back until the torso is nearly parallel, then stands up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: standing hip hinge with hands behind the head: knees slightly bent, pushes the hips back with a flat back until the torso is nearly parallel to the floor, then stands up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">hip_thrust</t>
@@ -364,7 +367,7 @@
     <t xml:space="preserve">Costas apoiadas no banco; no topo, estenda uma perna reta antes de descer.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a hip thrust with leg extension: upper back on a bench, dumbbell on the hips, drives the hips up, extends one leg straight at the top, puts it down and lowers. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: hip thrust with leg extension: upper back on a bench, dumbbell on the hips, drives the hips up, extends one leg straight at the top, puts it down and lowers. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">ponte</t>
@@ -376,7 +379,7 @@
     <t xml:space="preserve">Deitada(o), pés no chão, suba o quadril apertando o glúteo e segure 1 segundo no topo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a glute bridge: lying on the back with knees bent and feet on the floor, lifts the hips squeezing the glutes, holds one second at the top and lowers. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: glute bridge: lying on the back with knees bent and feet on the floor, lifts the hips squeezing the glutes, holds one second at the top and lowers. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">ponte_iso</t>
@@ -388,7 +391,7 @@
     <t xml:space="preserve">Suba o quadril e segure lá em cima, apertando o glúteo o tempo todo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs a steady isometric glute bridge hold: lying on the back, hips lifted and glutes squeezed, holding at the top. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: isometric glute bridge hold: lying on the back, hips lifted and glutes squeezed, holding at the top. The person holds the position still for the whole clip, breathing calmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">ponte_uni</t>
@@ -400,7 +403,7 @@
     <t xml:space="preserve">Uma perna estendida no ar, suba o quadril sem deixar a pelve girar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-leg glute bridge: lying on the back, one leg extended in the air, lifts the hips with the other leg keeping the pelvis level, then lowers. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: single-leg glute bridge: lying on the back, one leg extended in the air, lifts the hips with the other leg keeping the pelvis level, then lowers. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">stiff_halter</t>
@@ -421,7 +424,7 @@
     <t xml:space="preserve">Halteres na frente das coxas, desça levando o quadril pra trás até sentir a parte de trás da coxa.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a dumbbell romanian deadlift: dumbbells in front of the thighs, pushes the hips back until a hamstring stretch, stands up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: dumbbell romanian deadlift: dumbbells in front of the thighs, pushes the hips back until a hamstring stretch, stands up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">stiff_remada</t>
@@ -433,7 +436,7 @@
     <t xml:space="preserve">Desça em stiff e, no ponto mais baixo, puxe os halteres abrindo os braços em remada.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a romanian deadlift to wide row: holding dumbbells, hinges at the hips with a flat back, at the bottom rows the dumbbells with elbows flared wide, lowers and stands up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: romanian deadlift to wide row: holding dumbbells, hinges at the hips with a flat back, at the bottom rows the dumbbells with elbows flared wide, lowers and stands up. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">stiff_uni</t>
@@ -451,7 +454,7 @@
     <t xml:space="preserve">Apoiada(o) numa perna, leve o tronco à frente e a outra perna pra trás, formando uma linha.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-leg romanian deadlift: balancing on one leg, tips the torso forward while the other leg extends straight back forming a T, then returns upright. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: single-leg romanian deadlift: balancing on one leg, tips the torso forward while the other leg extends straight back forming a T, then returns upright. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">afundo_elev</t>
@@ -469,7 +472,7 @@
     <t xml:space="preserve">Desça no afundo e, ao subir, eleve os braços lateralmente até a linha do ombro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a lunge into lateral raise: holding light dumbbells, lunges, and when standing up raises both arms out to shoulder height. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: lunge into lateral raise: holding light dumbbells, lunges, and when standing up raises both arms out to shoulder height. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">afundo</t>
@@ -481,7 +484,7 @@
     <t xml:space="preserve">Passo largo, joelho de trás desce em direção ao chão, tronco ereto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a alternating forward lunge: long step forward, back knee lowers toward the floor with an upright torso, pushes back and alternates legs. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: alternating forward lunge: long step forward, back knee lowers toward the floor with an upright torso, pushes back and alternates legs. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">bulgaro</t>
@@ -502,7 +505,7 @@
     <t xml:space="preserve">Pé de trás no banco; na posição mais baixa, empurre os halteres pra cima.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a bulgarian split squat with shoulder press: rear foot on a bench, dumbbells at shoulders, lowers into the split squat and presses overhead at the bottom. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: bulgarian split squat with shoulder press: rear foot on a bench, dumbbells at shoulders, lowers into the split squat and presses overhead at the bottom. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">afundo_salto</t>
@@ -514,7 +517,7 @@
     <t xml:space="preserve">Do afundo, salte e troque as pernas no ar, aterrissando macio.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a jumping lunge: from a lunge, jumps and switches legs in the air, lands softly in the opposite lunge. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: jumping lunge: from a lunge, jumps and switches legs in the air, lands softly in the opposite lunge. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">afundo_iso</t>
@@ -529,7 +532,7 @@
     <t xml:space="preserve">Desça no afundo e segure lá embaixo, tronco ereto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs a steady isometric lunge hold: lowers into a lunge and holds at the bottom with an upright torso. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: isometric lunge hold: lowers into a lunge and holds at the bottom with an upright torso. The person holds the position still for the whole clip, breathing calmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">afundo_lat</t>
@@ -544,7 +547,7 @@
     <t xml:space="preserve">Passo largo pro lado, quadril pra trás, a outra perna fica estendida.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a lateral lunge: big step to the side, sits the hips back over the bent leg while the other leg stays straight, pushes back to center. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: lateral lunge: big step to the side, sits the hips back over the bent leg while the other leg stays straight, pushes back to center. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">afundo_rev</t>
@@ -556,7 +559,7 @@
     <t xml:space="preserve">Desça no afundo pra trás e suba levando o joelho até a altura do quadril, como na passada.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a reverse lunge to knee drive: steps back into a reverse lunge, drives up and brings the back knee to hip height like a running stride. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: reverse lunge to knee drive: steps back into a reverse lunge, drives up and brings the back knee to hip height like a running stride. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">step_up</t>
@@ -571,7 +574,7 @@
     <t xml:space="preserve">Suba empurrando pelo calcanhar da perna de cima, sem dar impulso com a de baixo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a step-up: places one foot on a box and drives up through the heel without pushing off the bottom leg, then steps down. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: step-up: places one foot on a box and drives up through the heel without pushing off the bottom leg, then steps down. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">step_chute</t>
@@ -586,7 +589,7 @@
     <t xml:space="preserve">No topo do step, estenda a perna de trás antes de descer.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a step-up with back kick: steps onto a box, at the top extends the free leg straight back squeezing the glute, then steps down. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: step-up with back kick: steps onto a box, at the top extends the free leg straight back squeezing the glute, then steps down. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">desenv_el</t>
@@ -607,7 +610,7 @@
     <t xml:space="preserve">Pise no elástico e empurre pra cima, controlando a volta.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a resistance band shoulder press: standing on a resistance band, presses the handles overhead and lowers them with control. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: resistance band shoulder press: standing on a resistance band, presses the handles overhead and lowers them with control. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">desenv</t>
@@ -622,7 +625,7 @@
     <t xml:space="preserve">Em pé, abdômen firme, empurre os halteres acima da cabeça sem arquear a lombar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a standing dumbbell shoulder press: dumbbells at shoulder height, core tight, presses them overhead without arching the lower back, then lowers. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: standing dumbbell shoulder press: dumbbells at shoulder height, core tight, presses them overhead without arching the lower back, then lowers. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">desenv_uni</t>
@@ -643,7 +646,7 @@
     <t xml:space="preserve">Um braço de cada vez, abdômen firme pra o tronco não inclinar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-arm dumbbell shoulder press: presses one dumbbell overhead with the core tight so the torso stays upright, then lowers. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: single-arm dumbbell shoulder press: presses one dumbbell overhead with the core tight so the torso stays upright, then lowers. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">elev_lat</t>
@@ -661,7 +664,7 @@
     <t xml:space="preserve">Cotovelos levemente dobrados, suba os braços até a linha do ombro sem balançar o tronco.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a dumbbell lateral raise: elbows slightly bent, raises the arms out to shoulder height without swinging the torso. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: dumbbell lateral raise: elbows slightly bent, raises the arms out to shoulder height without swinging the torso. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">flex_pausa</t>
@@ -679,7 +682,7 @@
     <t xml:space="preserve">Desça devagar, pare 2 segundos perto do chão e empurre de volta.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pause push-up: lowers slowly, pauses two seconds just above the floor, pushes back up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: pause push-up: lowers slowly, pauses two seconds just above the floor, pushes back up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">flex_rot</t>
@@ -691,7 +694,7 @@
     <t xml:space="preserve">Flexão completa e, ao subir, gire o tronco levando um braço pro teto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a push-up to T rotation: full push-up, then rotates the body opening one arm straight up to the ceiling, returns to plank and alternates sides. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: push-up to T rotation: full push-up, then rotates the body opening one arm straight up to the ceiling, returns to plank and alternates sides. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">flex_joelho</t>
@@ -703,7 +706,7 @@
     <t xml:space="preserve">Joelhos no chão, quadril alinhado com o tronco, cotovelos a 45° do corpo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a knee push-up: knees on the mat, hips aligned with the torso, elbows at 45 degrees, lowers the chest toward the floor and pushes up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: knee push-up: knees on the mat, hips aligned with the torso, elbows at 45 degrees, lowers the chest toward the floor and pushes up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">flex_explosiva</t>
@@ -718,7 +721,7 @@
     <t xml:space="preserve">Mãos num banco ou mesa firme; empurre rápido a ponto de as mãos saírem do apoio.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a explosive incline push-up: hands on a sturdy bench, pushes up fast enough that the hands briefly leave the bench, lands softly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: explosive incline push-up: hands on a sturdy bench, pushes up fast enough that the hands briefly leave the bench, lands softly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">flex_incl</t>
@@ -730,7 +733,7 @@
     <t xml:space="preserve">Mãos num banco, mesa firme ou parede; corpo reto, desça o peito até perto do apoio.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a incline push-up: hands on a sturdy bench, body in a straight line, lowers the chest close to the bench and pushes back up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: incline push-up: hands on a sturdy bench, body in a straight line, lowers the chest close to the bench and pushes back up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">triceps_banco</t>
@@ -745,7 +748,7 @@
     <t xml:space="preserve">Mãos no banco atrás do corpo, desça dobrando os cotovelos pra trás e suba.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a bench dip: hands on a bench behind the body, bends the elbows straight back to lower, then pushes up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: bench dip: hands on a bench behind the body, bends the elbows straight back to lower, then pushes up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">supino_abd</t>
@@ -763,7 +766,7 @@
     <t xml:space="preserve">Supino completo deitada(o) no chão e, sem descansar, um abdominal.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a dumbbell floor press into sit-up: lying on a mat, presses two dumbbells up from the chest, lowers them, then immediately performs a sit-up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: dumbbell floor press into sit-up: lying on a mat, presses two dumbbells up from the chest, lowers them, then immediately performs a sit-up. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">triceps_halter</t>
@@ -778,7 +781,7 @@
     <t xml:space="preserve">Segure o halter com as duas mãos atrás da cabeça e estenda os braços, cotovelos apontando pra frente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a dumbbell overhead triceps extension: holds one dumbbell with both hands behind the head and extends the arms, elbows pointing forward. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: dumbbell overhead triceps extension: holds one dumbbell with both hands behind the head and extends the arms, elbows pointing forward. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">ytw</t>
@@ -796,7 +799,7 @@
     <t xml:space="preserve">De barriga pra baixo, eleve os braços formando Y, depois T, depois W, apertando as escápulas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a prone Y-T-W raises: lying face down, lifts the arms forming a Y, then a T, then a W, squeezing the shoulder blades each time. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: prone Y-T-W raises: lying face down, lifts the arms forming a Y, then a T, then a W, squeezing the shoulder blades each time. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">puxada_alta_exp</t>
@@ -808,7 +811,7 @@
     <t xml:space="preserve">Impulso do quadril e puxe o peso rápido até a altura do peito, cotovelos altos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a explosive dumbbell high pull: hinged slightly, drives the hips forward and pulls the weight fast to chest height with high elbows. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: explosive dumbbell high pull: hinged slightly, drives the hips forward and pulls the weight fast to chest height with high elbows. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">barra_aus</t>
@@ -823,7 +826,7 @@
     <t xml:space="preserve">Pendurada(o) embaixo de uma barra baixa, corpo reto, puxe o peito até a barra.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a inverted row: hanging under a low bar with a straight body and heels on the floor, pulls the chest up to the bar and lowers. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: inverted row: hanging under a low bar with a straight body and heels on the floor, pulls the chest up to the bar and lowers. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">remada_el</t>
@@ -835,7 +838,7 @@
     <t xml:space="preserve">Sentada(o), elástico nos pés, puxe os cotovelos pra trás rente ao corpo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a seated resistance band row: sitting on the floor with legs extended and the band around the feet, pulls the elbows back close to the body. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: seated resistance band row: sitting on the floor with legs extended and the band around the feet, pulls the elbows back close to the body. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">remada_pausa</t>
@@ -856,7 +859,7 @@
     <t xml:space="preserve">Puxe, segure 2 segundos com as escápulas apertadas e volte devagar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pause dumbbell row: hinged forward, rows the dumbbells, holds two seconds squeezing the shoulder blades, lowers slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: pause dumbbell row: hinged forward, rows the dumbbells, holds two seconds squeezing the shoulder blades, lowers slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">remada_rot</t>
@@ -874,7 +877,7 @@
     <t xml:space="preserve">Puxe o halter em remada e, no topo, gire o tronco levando o cotovelo pro teto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a bent-over row with torso rotation: hinged forward with a flat back, rows a single dumbbell, rotates the torso opening the elbow toward the ceiling, then lowers. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: bent-over row with torso rotation: hinged forward with a flat back, rows a single dumbbell, rotates the torso opening the elbow toward the ceiling, then lowers. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">renegade</t>
@@ -889,7 +892,7 @@
     <t xml:space="preserve">Prancha firme, quadril estável, puxe o halter sem girar o tronco.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a renegade row: high plank with hands on two dumbbells and feet wide, rows one dumbbell to the hip without rotating the hips, alternates arms. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: renegade row: high plank with hands on two dumbbells and feet wide, rows one dumbbell to the hip without rotating the hips, alternates arms. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">remada_uni</t>
@@ -901,7 +904,7 @@
     <t xml:space="preserve">Uma mão e um joelho apoiados, puxe o halter em direção ao quadril.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-arm dumbbell row: one hand and one knee supported on a bench, rows the dumbbell toward the hip and lowers it. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: single-arm dumbbell row: one hand and one knee supported on a bench, rows the dumbbell toward the hip and lowers it. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">remada_el_uni</t>
@@ -916,7 +919,7 @@
     <t xml:space="preserve">Um braço de cada vez, cotovelo rente ao corpo, sem girar o tronco.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-arm resistance band row: band anchored in front, rows one arm with the elbow close to the body without twisting the torso. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: single-arm resistance band row: band anchored in front, rows one arm with the elbow close to the body without twisting the torso. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">rosca_alt</t>
@@ -934,7 +937,7 @@
     <t xml:space="preserve">Um braço de cada vez, girando a palma pra cima enquanto sobe.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a alternating dumbbell curl: one arm at a time, rotating the palm up while curling. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: alternating dumbbell curl: one arm at a time, rotating the palm up while curling. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">rosca_el</t>
@@ -946,7 +949,7 @@
     <t xml:space="preserve">Pise no elástico, cotovelos parados ao lado do corpo, suba as mãos até os ombros.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a resistance band biceps curl: standing on the band, elbows still at the sides, curls the hands up to the shoulders. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: resistance band biceps curl: standing on the band, elbows still at the sides, curls the hands up to the shoulders. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">rosca_martelo</t>
@@ -958,7 +961,7 @@
     <t xml:space="preserve">Palmas viradas uma pra outra o tempo todo, cotovelos parados.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a hammer curl: palms facing each other throughout, elbows still, curls the dumbbells up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: neutral-grip dumbbell curl: palms facing each other throughout, elbows still at the sides, curls the dumbbells up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">superman</t>
@@ -970,7 +973,7 @@
     <t xml:space="preserve">De barriga pra baixo, braços estendidos à frente; puxe os cotovelos em direção ao corpo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a superman pull: lying face down with arms extended forward, lifts chest and arms and pulls the elbows back toward the ribs, then reaches forward again. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: prone back extension with arm pull: lying face down with arms extended forward, lifts chest and arms slightly and pulls the elbows back toward the ribs, then reaches forward again. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">superman_iso</t>
@@ -985,7 +988,7 @@
     <t xml:space="preserve">De barriga pra baixo, tire braços e peito do chão e segure, apertando as escápulas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs a steady isometric superman hold: lying face down, lifts arms and chest off the floor and holds, squeezing the shoulder blades. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: prone back extension hold: lying face down on the mat, lifts arms and chest off the floor and holds still, squeezing the shoulder blades. The person holds the position still for the whole clip, breathing calmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">abd_lado</t>
@@ -1003,7 +1006,7 @@
     <t xml:space="preserve">Perna de baixo dobrada, suba a de cima reta e levemente pra trás, sem girar o quadril.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a side-lying hip abduction: bottom leg bent, lifts the straight top leg slightly behind the body without rotating the hips. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: side-lying hip abduction: bottom leg bent, lifts the straight top leg slightly behind the body without rotating the hips. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">dead_bug</t>
@@ -1015,7 +1018,7 @@
     <t xml:space="preserve">Deitada(o) de costas, estenda braço e perna opostos sem tirar a lombar do chão.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a dead bug: lying on the back with arms up and knees at 90 degrees, extends the opposite arm and leg while the lower back stays on the floor, alternates. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: lying on the back with arms pointing up and knees bent at 90 degrees, slowly extends the opposite arm and leg toward the floor while the lower back stays flat, then alternates sides. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">pallof</t>
@@ -1036,7 +1039,7 @@
     <t xml:space="preserve">De lado pro elástico ou polia, empurre as mãos pra frente sem deixar o tronco girar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pallof press: standing sideways to a resistance band anchored at chest height, presses the hands forward without letting the torso rotate. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: standing sideways to a resistance band anchored at chest height, holds the band at the chest and presses the hands straight forward without letting the torso rotate. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">hollow</t>
@@ -1048,7 +1051,7 @@
     <t xml:space="preserve">Deitada(o) de costas, tire ombros e pernas do chão com a lombar colada no chão.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs a steady hollow body hold: lying on the back, lifts shoulders and legs off the floor with the lower back pressed into the floor, holding. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: lying on the back, lifts the shoulders and straight legs slightly off the floor with arms extended overhead and the lower back pressed into the floor, holding still. The person holds the position still for the whole clip, breathing calmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">equil_uni</t>
@@ -1063,7 +1066,7 @@
     <t xml:space="preserve">Numa perna só, incline o tronco e alcance o chão à frente, voltando devagar e sem deixar o joelho cair pra dentro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-leg balance reach: on one leg, hinges forward reaching toward the floor in front, returns slowly keeping the knee aligned. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: single-leg balance reach: on one leg, hinges forward reaching toward the floor in front, returns slowly keeping the knee aligned. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">woodchop</t>
@@ -1081,7 +1084,7 @@
     <t xml:space="preserve">Gire de um ombro até o quadril oposto usando a rotação do tronco.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a dumbbell woodchopper: holding one dumbbell with both hands above one shoulder, chops diagonally down to the opposite hip by rotating the torso, then returns. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: diagonal torso rotation with one dumbbell: holding the dumbbell with both hands above one shoulder, rotates and brings it diagonally down to the outside of the opposite hip, then returns. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">ostra</t>
@@ -1099,7 +1102,7 @@
     <t xml:space="preserve">Deitada(o) de lado, joelhos dobrados, abra o joelho de cima sem girar o quadril.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a clamshell: lying on the side with knees bent, opens the top knee without rolling the hips back, closes it. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: lying on the side with knees bent and feet together, opens the top knee upward without rolling the hips back, then closes it. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">bird_dog</t>
@@ -1111,7 +1114,7 @@
     <t xml:space="preserve">Em quatro apoios, estenda braço e perna opostos e segure 2 segundos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a bird dog: on hands and knees, extends the opposite arm and leg, holds two seconds, returns and alternates. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: on hands and knees on the mat, extends the opposite arm forward and leg back, holds two seconds, returns and alternates sides. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">prancha</t>
@@ -1123,7 +1126,7 @@
     <t xml:space="preserve">Corpo alinhado da cabeça aos calcanhares, abdômen contraído.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs a steady forearm plank hold: forearms on the mat, body in a straight line from head to heels, core braced, holding still. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: forearm plank hold: forearms on the mat, body in a straight line from head to heels, core braced, holding still. The person holds the position still for the whole clip, breathing calmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">thread</t>
@@ -1135,7 +1138,7 @@
     <t xml:space="preserve">Gire o tronco levando um braço por baixo do corpo e depois pro teto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a plank thread the needle: from a high plank, reaches one arm under the body rotating the torso, then opens it up toward the ceiling. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: from a high plank, reaches one arm under the body rotating the torso, then opens the same arm up toward the ceiling, hips stay stable. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">plank_jack</t>
@@ -1147,7 +1150,7 @@
     <t xml:space="preserve">Prancha alta; abra e feche os pés saltando, sem deixar o quadril subir.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs a steady plank jacks: high plank, jumps the feet open and closed while keeping the hips level. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: from a high plank, jumps the feet wide apart and back together repeatedly while the hips stay level. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">prancha_toque</t>
@@ -1159,7 +1162,7 @@
     <t xml:space="preserve">Quadril estável, sem balançar o tronco ao tocar o ombro oposto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs a steady high plank shoulder taps: in a high plank, alternately taps the opposite shoulder with one hand while keeping the hips still. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: high plank shoulder taps: in a high plank, alternately taps the opposite shoulder with one hand while keeping the hips still. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">prancha_lat</t>
@@ -1174,7 +1177,7 @@
     <t xml:space="preserve">Apoio no antebraço, quadril alto, corpo em linha reta.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs a steady side plank hold: on one forearm, hips lifted high, body in a straight line, holding still. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 6 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: side plank hold: on one forearm, hips lifted high, body in a straight line, holding still. The person holds the position still for the whole clip, breathing calmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">prancha_abd</t>
@@ -1189,7 +1192,7 @@
     <t xml:space="preserve">Na prancha lateral, suba e desça a perna de cima devagar, com o quadril alto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a side plank with leg lift: in a side plank with high hips, raises and lowers the top leg slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: side plank with leg lift: in a side plank with high hips, raises and lowers the top leg slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">russian</t>
@@ -1207,7 +1210,7 @@
     <t xml:space="preserve">Tronco levemente inclinado pra trás, gire pela rotação do tronco, não só dos braços.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a seated russian twist: sitting with knees bent and torso leaning slightly back, hands together, rotates the torso side to side. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: seated torso rotation: sitting on the mat with knees bent and torso leaning slightly back, hands clasped together, rotates the torso side to side. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">agacho_salto_dev</t>
@@ -1222,7 +1225,7 @@
     <t xml:space="preserve">Agache, exploda num salto e, ao aterrissar, empurre os halteres pra cima.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a squat jump into shoulder press: light dumbbells at shoulders, squats, jumps, lands softly and presses the dumbbells overhead. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: squat jump into shoulder press: light dumbbells at shoulders, squats, jumps, lands softly and presses the dumbbells overhead. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">thruster</t>
@@ -1234,7 +1237,7 @@
     <t xml:space="preserve">Agache completo e use o impulso das pernas pra empurrar o peso pra cima.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a dumbbell thruster: dumbbells at the shoulders, full squat, then uses the leg drive to press the dumbbells overhead in one fluid motion. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: dumbbell thruster: dumbbells at the shoulders, full squat, then uses the leg drive to press the dumbbells overhead in one fluid motion. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">burpee</t>
@@ -1246,7 +1249,7 @@
     <t xml:space="preserve">Agache, mãos no chão, pés pra trás, volte e salte com os braços pra cima.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a burpee: squats, places hands on the floor, jumps the feet back to plank, jumps them back in and jumps up with arms overhead. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: burpee: squats, places hands on the floor, jumps the feet back to plank, jumps them back in and jumps up with arms overhead. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">devil</t>
@@ -1261,7 +1264,7 @@
     <t xml:space="preserve">Mãos no halter, pés pra trás em prancha, volte e leve o halter do chão até acima da cabeça.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 2 clean repetitions of a dumbbell devil press: hands on two dumbbells, jumps feet back to plank and lowers the chest, jumps in, then swings both dumbbells from the floor to overhead. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 10 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: hands on two dumbbells on the floor, jumps the feet back into a plank and lowers the chest, jumps the feet back in, then swings both dumbbells from the floor to overhead in one continuous motion. The person performs 2 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">mountain</t>
@@ -1273,7 +1276,7 @@
     <t xml:space="preserve">Prancha alta, traga os joelhos ao peito alternando, quadril baixo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs a continuous mountain climbers: high plank, drives the knees to the chest alternately at a fast pace with low hips. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: from a high plank, drives the knees to the chest alternately at a fast running pace, hips low. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">mountain_toque</t>
@@ -1285,7 +1288,7 @@
     <t xml:space="preserve">A cada 4 repetições, toque o ombro oposto sem perder o ritmo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs a continuous mountain climbers with shoulder taps: fast mountain climbers and every four reps taps the opposite shoulder. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: from a high plank, drives the knees to the chest alternately at a fast pace, and every four knee drives taps the opposite shoulder with one hand. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">marcha</t>
@@ -1300,7 +1303,7 @@
     <t xml:space="preserve">Joelhos altos e braços ativos, sem saltar — cardio sem impacto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs a continuous fast high-knee march in place: lifts the knees high with active arms, no jumping. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: fast high-knee march in place: lifts the knees high with active arms, no jumping. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">lateral_pausa</t>
@@ -1315,7 +1318,7 @@
     <t xml:space="preserve">Passo largo e rápido pro lado e equilibre 2 segundos numa perna antes de voltar. Sem salto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a lateral step with balance pause: quick wide step to the side, balances two seconds on one leg, then steps back, no jumping. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: lateral step with balance pause: quick wide step to the side, balances two seconds on one leg, then steps back, no jumping. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">polichinelo</t>
@@ -1327,7 +1330,7 @@
     <t xml:space="preserve">Aterrisse leve, na ponta dos pés, ritmo constante.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs a continuous jumping jacks: jumps opening the legs while raising the arms overhead, lands softly on the balls of the feet, steady rhythm. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: jumping in place opening the legs while raising the arms overhead, then closing, landing softly on the balls of the feet, steady rhythm. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">pogo</t>
@@ -1342,7 +1345,7 @@
     <t xml:space="preserve">Pulos curtos e rápidos só com o tornozelo, joelhos quase estendidos, tocando o chão com a ponta do pé.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pogo hops: short, quick hops using only the ankles, knees almost straight, landing on the balls of the feet. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: small quick bounces in place using only the ankles, knees almost straight, landing on the balls of the feet. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">skater</t>
@@ -1354,7 +1357,7 @@
     <t xml:space="preserve">Salte de lado pousando na perna oposta, cruzando a de trás.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a skater jumps: leaps sideways from one leg and lands softly on the other, sweeping the trailing leg behind. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: lateral bounds: jumps sideways from one leg and lands softly on the other leg, sweeping the trailing leg behind, then bounds back. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">salto_caixote</t>
@@ -1369,7 +1372,7 @@
     <t xml:space="preserve">Agache um pouco, salte com os dois pés e aterrisse macio no meio do caixote. Desça andando.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a box jump: small squat, jumps with both feet and lands softly in the middle of a box, steps down. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: box jump: small squat, jumps with both feet and lands softly in the middle of a box, steps down. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">salto_uni</t>
@@ -1384,7 +1387,7 @@
     <t xml:space="preserve">Impulsione numa perna, aterrisse na mesma perna e segure 2 segundos equilibrada(o).</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-leg forward hop: hops forward off one leg, lands on the same leg and holds balance two seconds. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: single-leg forward hop: hops forward off one leg, lands on the same leg and holds balance two seconds. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">salto_lat</t>
@@ -1396,7 +1399,7 @@
     <t xml:space="preserve">Pés juntos, salte de um lado pro outro da linha, leve e rápido.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs a continuous lateral line hops: feet together, hops side to side over a line on the floor, light and fast. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a bright minimal studio with a light gray background, on a black exercise mat. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: lateral line hops: feet together, hops side to side over a line on the floor, light and fast. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Academia</t>
@@ -1417,7 +1420,7 @@
     <t xml:space="preserve">Barra apoiada no alto das costas, abdômen travado, desça até a coxa ficar paralela ao chão.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a barbell back squat: bar on the upper back, core braced, squats until thighs are parallel, then stands up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: barbell back squat: bar on the upper back, core braced, squats until thighs are parallel, then stands up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">hack</t>
@@ -1429,7 +1432,7 @@
     <t xml:space="preserve">Costas inteiras no apoio, desça controlando e suba empurrando o chão com o pé todo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a hack squat machine: back fully on the pad, lowers with control and pushes up through the whole foot. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: hack squat machine: back fully on the pad, lowers with control and pushes up through the whole foot. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">smith</t>
@@ -1441,7 +1444,7 @@
     <t xml:space="preserve">Pés um pouco à frente da barra, desça como quem senta, tronco firme.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a smith machine squat: feet slightly in front of the bar, sits down with a firm torso and stands up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: smith machine squat: feet slightly in front of the bar, sits down with a firm torso and stands up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">extensora</t>
@@ -1453,7 +1456,7 @@
     <t xml:space="preserve">Estenda as pernas até em cima, segure 1 segundo e desça devagar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a leg extension machine: extends the legs fully, holds one second at the top, lowers slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: leg extension machine: extends the legs fully, holds one second at the top, lowers slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">leg_press</t>
@@ -1465,7 +1468,7 @@
     <t xml:space="preserve">Pés na largura do quadril no meio da plataforma; desça até uns 90° nos joelhos sem tirar a lombar do encosto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a 45-degree leg press machine: feet hip-width in the middle of the platform, lowers to about 90 degrees at the knees, lower back on the pad, pushes up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: 45-degree leg press machine: feet hip-width in the middle of the platform, lowers to about 90 degrees at the knees, lower back on the pad, pushes up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">leg_press_pausa</t>
@@ -1480,7 +1483,7 @@
     <t xml:space="preserve">Desça controlando, segure 2 segundos lá embaixo e suba firme.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pause leg press: lowers with control, holds two seconds at the bottom, pushes up firmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: pause leg press: lowers with control, holds two seconds at the bottom, pushes up firmly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">leg_press_uni</t>
@@ -1498,7 +1501,7 @@
     <t xml:space="preserve">Uma perna de cada vez no centro da plataforma, sem deixar o joelho cair pra dentro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-leg leg press: one foot in the center of the platform, lowers and pushes without letting the knee cave in. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: single-leg leg press: one foot in the center of the platform, lowers and pushes without letting the knee cave in. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">pant_pe</t>
@@ -1510,7 +1513,7 @@
     <t xml:space="preserve">Pernas quase estendidas, suba na ponta do pé e desça devagar até alongar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a standing calf raise machine: legs almost straight, rises onto the toes and lowers slowly into a stretch. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: standing calf raise machine: legs almost straight, rises onto the toes and lowers slowly into a stretch. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">pant_sentado</t>
@@ -1525,7 +1528,7 @@
     <t xml:space="preserve">Suba na ponta do pé o máximo que der, segure 1 segundo e desça alongando.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a seated calf raise machine: rises onto the toes as high as possible, holds one second, lowers into a stretch. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: seated calf raise machine: rises onto the toes as high as possible, holds one second, lowers into a stretch. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">abducao</t>
@@ -1537,7 +1540,7 @@
     <t xml:space="preserve">Abra as pernas empurrando com a lateral do quadril, segure 1 segundo e volte devagar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a hip abduction machine: seated, pushes the legs apart with the outer hips, holds one second, returns slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: hip abduction machine: seated, pushes the legs apart with the outer hips, holds one second, returns slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">flexora</t>
@@ -1549,7 +1552,7 @@
     <t xml:space="preserve">Joelho alinhado com o eixo da máquina, puxe os calcanhares pra baixo e volte devagar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a seated leg curl machine: knee aligned with the machine axis, pulls the heels down and returns slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: seated leg curl machine: knee aligned with the machine axis, pulls the heels down and returns slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">flexora_uni</t>
@@ -1564,7 +1567,7 @@
     <t xml:space="preserve">Uma perna de cada vez, sem girar o quadril.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-leg seated leg curl: one leg at a time on the machine, curls without twisting the hips. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: single-leg seated leg curl: one leg at a time on the machine, curls without twisting the hips. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">coice_polia</t>
@@ -1579,7 +1582,7 @@
     <t xml:space="preserve">Tronco levemente inclinado, leve a perna pra trás sem arquear a lombar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a cable glute kickback: ankle strap on a low cable, torso slightly leaning forward, kicks one leg back without arching the lower back. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: cable glute kickback: ankle strap on a low cable, torso slightly leaning forward, kicks one leg back without arching the lower back. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">hip_barra</t>
@@ -1591,7 +1594,7 @@
     <t xml:space="preserve">Costas no banco, barra no quadril (com proteção); suba até o tronco ficar reto, queixo pra baixo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a barbell hip thrust: upper back on a bench, padded barbell on the hips, drives up until the torso is straight, chin tucked. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: barbell hip thrust: upper back on a bench, padded barbell on the hips, drives up until the torso is straight, chin tucked. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">hip_barra_pausa</t>
@@ -1609,7 +1612,7 @@
     <t xml:space="preserve">Suba e segure 2 segundos lá em cima apertando o glúteo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pause barbell hip thrust: drives the hips up and holds two seconds at the top squeezing the glutes, lowers. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: pause barbell hip thrust: drives the hips up and holds two seconds at the top squeezing the glutes, lowers. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">elev_quadril_maq</t>
@@ -1621,7 +1624,7 @@
     <t xml:space="preserve">Suba o quadril até alinhar com o tronco, segure 1 segundo apertando o glúteo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a hip thrust machine: drives the hips up until aligned with the torso, holds one second squeezing the glutes, lowers. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: hip thrust machine: drives the hips up until aligned with the torso, holds one second squeezing the glutes, lowers. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">terra_sumo</t>
@@ -1633,7 +1636,7 @@
     <t xml:space="preserve">Pés bem afastados, mãos por dentro das pernas, suba empurrando o chão e apertando o glúteo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a sumo deadlift with barbell: very wide stance, hands inside the legs, stands up pushing the floor and squeezing the glutes. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: sumo deadlift with barbell: very wide stance, hands inside the legs, stands up pushing the floor and squeezing the glutes. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">mesa_flexora</t>
@@ -1645,7 +1648,7 @@
     <t xml:space="preserve">Quadril colado no banco, traga os calcanhares em direção ao glúteo sem tirar o quadril.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a lying leg curl machine: hips pressed into the bench, curls the heels toward the glutes, lowers slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: lying leg curl machine: hips pressed into the bench, curls the heels toward the glutes, lowers slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">stiff_barra</t>
@@ -1657,7 +1660,7 @@
     <t xml:space="preserve">Barra rente às pernas, joelhos levemente dobrados, leve o quadril pra trás com as costas retas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a barbell romanian deadlift: bar close to the legs, knees slightly bent, hinges the hips back with a flat back, stands up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: barbell romanian deadlift: bar close to the legs, knees slightly bent, hinges the hips back with a flat back, stands up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">stiff_polia</t>
@@ -1669,7 +1672,7 @@
     <t xml:space="preserve">De frente pra polia baixa, leve o quadril pra trás com as costas retas e suba apertando o glúteo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a cable pull-through romanian deadlift: facing a low cable, hinges the hips back with a flat back, stands up squeezing the glutes. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: cable pull-through romanian deadlift: facing a low cable, hinges the hips back with a flat back, stands up squeezing the glutes. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">afundo_smith</t>
@@ -1681,7 +1684,7 @@
     <t xml:space="preserve">Passo largo, desça reto até o joelho de trás quase tocar o chão; a barra guia o movimento.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a smith machine lunge: long split stance under the bar, lowers straight down until the back knee nearly touches the floor. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: smith machine lunge: long split stance under the bar, lowers straight down until the back knee nearly touches the floor. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">bulgaro_h</t>
@@ -1696,7 +1699,7 @@
     <t xml:space="preserve">Pé de trás apoiado no banco, desça reto com o tronco firme.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a dumbbell bulgarian split squat: rear foot on a bench, dumbbells at the sides, lowers straight down with a firm torso. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: dumbbell bulgarian split squat: rear foot on a bench, dumbbells at the sides, lowers straight down with a firm torso. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">crucifixo</t>
@@ -1708,7 +1711,7 @@
     <t xml:space="preserve">Cotovelos levemente dobrados, junte os braços na frente do peito e volte devagar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pec deck machine fly: elbows slightly bent, brings the arms together in front of the chest and returns slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: seated chest fly machine: elbows slightly bent, brings the arms together in front of the chest and returns slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">desenv_barra</t>
@@ -1720,7 +1723,7 @@
     <t xml:space="preserve">Em pé, glúteo e abdômen firmes, empurre a barra acima da cabeça passando rente ao rosto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a standing barbell overhead press: glutes and core tight, presses the bar overhead close to the face. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: standing barbell overhead press: glutes and core tight, presses the bar overhead close to the face. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">desenv_maq</t>
@@ -1732,7 +1735,7 @@
     <t xml:space="preserve">Costas no encosto, empurre pra cima sem arquear a lombar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a machine shoulder press: back against the pad, presses up without arching the lower back. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: machine shoulder press: back against the pad, presses up without arching the lower back. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">supino_pausa</t>
@@ -1750,7 +1753,7 @@
     <t xml:space="preserve">Desça, segure 1 segundo encostando de leve no peito e empurre firme.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pause barbell bench press: lowers the bar, pauses one second lightly touching the chest, presses up firmly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: pause barbell bench press: lowers the bar, pauses one second lightly touching the chest, presses up firmly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">supino_incl_h</t>
@@ -1762,7 +1765,7 @@
     <t xml:space="preserve">Banco inclinado, desça os halteres ao lado do peito e empurre pra cima juntando no topo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a incline dumbbell press: on an incline bench, lowers dumbbells beside the chest and presses up bringing them together at the top. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: incline dumbbell press: on an incline bench, lowers dumbbells beside the chest and presses up bringing them together at the top. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">supino_maq</t>
@@ -1774,7 +1777,7 @@
     <t xml:space="preserve">Pegada na linha do peito, empurre sem travar os cotovelos e volte devagar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a machine chest press: handles at chest line, presses forward without locking the elbows, returns slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: machine chest press: handles at chest line, presses forward without locking the elbows, returns slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">supino_polia</t>
@@ -1786,7 +1789,7 @@
     <t xml:space="preserve">Um pé à frente, empurre os puxadores pra frente juntando as mãos na altura do peito.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a standing cable chest press: one foot forward, presses the handles forward bringing the hands together at chest height. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: standing cable chest press: one foot forward, presses the handles forward bringing the hands together at chest height. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">supino_barra</t>
@@ -1798,7 +1801,7 @@
     <t xml:space="preserve">Escápulas apertadas no banco, desça a barra até o meio do peito e empurre.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a barbell bench press: shoulder blades pinched on the bench, lowers the bar to mid-chest and presses up. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: barbell bench press: shoulder blades pinched on the bench, lowers the bar to mid-chest and presses up. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">supino_uni_h</t>
@@ -1810,7 +1813,7 @@
     <t xml:space="preserve">Um halter só, abdômen firme pra não girar o tronco no banco.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-arm dumbbell bench press: one dumbbell only, core tight so the torso does not rotate on the bench. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: single-arm dumbbell bench press: one dumbbell only, core tight so the torso does not rotate on the bench. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">triceps_frances</t>
@@ -1822,7 +1825,7 @@
     <t xml:space="preserve">De costas pra polia, cotovelos apontando pra frente, estenda os braços acima da cabeça.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a overhead cable triceps extension: back to the cable, elbows pointing forward, extends the arms overhead. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: overhead cable triceps extension: back to the cable, elbows pointing forward, extends the arms overhead. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">triceps_corda</t>
@@ -1834,7 +1837,7 @@
     <t xml:space="preserve">Cotovelos colados no corpo, estenda os braços abrindo a corda no final.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a triceps rope pushdown: elbows tucked at the sides, extends the arms and spreads the rope at the bottom. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: triceps rope pushdown: elbows tucked at the sides, extends the arms and spreads the rope at the bottom. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">triceps_testa</t>
@@ -1846,7 +1849,7 @@
     <t xml:space="preserve">Cotovelos parados, leve a barra em direção à testa e estenda.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a cable skull crusher with bar: elbows still, lowers the bar toward the forehead and extends. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: lying cable triceps extension with a straight bar: lying on a bench, elbows still, lowers the bar toward the forehead and extends the arms. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">graviton</t>
@@ -1861,7 +1864,7 @@
     <t xml:space="preserve">Joelhos no apoio, puxe até o queixo passar a barra e desça controlando.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a assisted pull-up machine: knees on the assist pad, pulls up until the chin passes the bar, lowers with control. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: assisted pull-up machine: knees on the assist pad, pulls up until the chin passes the bar, lowers with control. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">crucifixo_inv</t>
@@ -1873,7 +1876,7 @@
     <t xml:space="preserve">Peito no apoio, abra os braços pra trás apertando a parte de trás do ombro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a reverse pec deck: chest on the pad, opens the arms back squeezing the rear shoulders. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: seated reverse fly machine: chest against the pad, opens the arms back squeezing the rear shoulders. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">pullover</t>
@@ -1885,7 +1888,7 @@
     <t xml:space="preserve">Braços quase estendidos, traga a barra do alto até as coxas usando as costas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a straight-arm cable pulldown: arms almost straight, sweeps the bar from overhead down to the thighs using the back. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: straight-arm cable pulldown: arms almost straight, sweeps the bar from overhead down to the thighs using the back. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">puxada_aberta</t>
@@ -1897,7 +1900,7 @@
     <t xml:space="preserve">Peito aberto, puxe a barra até a parte de cima do peito levando os cotovelos pra baixo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a wide-grip lat pulldown: chest up, pulls the bar to the upper chest driving the elbows down, returns with control. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: wide-grip lat pulldown: chest up, pulls the bar to the upper chest driving the elbows down, returns with control. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">puxada_pausa</t>
@@ -1915,7 +1918,7 @@
     <t xml:space="preserve">Puxe, segure 2 segundos apertando as costas e volte devagar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a pause lat pulldown: pulls the bar to the chest, holds two seconds squeezing the back, returns slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: pause lat pulldown: pulls the bar to the chest, holds two seconds squeezing the back, returns slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">puxada_tri</t>
@@ -1927,7 +1930,7 @@
     <t xml:space="preserve">Puxe o triângulo até o peito com os cotovelos rentes ao corpo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a close-grip lat pulldown with V-handle: pulls the handle to the chest with elbows close to the body. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: close-grip lat pulldown with V-handle: pulls the handle to the chest with elbows close to the body. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">face_pull</t>
@@ -1939,7 +1942,7 @@
     <t xml:space="preserve">Corda na altura do rosto, puxe abrindo os cotovelos e apertando as escápulas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a cable face pull with rope: rope at face height, pulls toward the face flaring the elbows and squeezing the shoulder blades. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: cable rope pull to face height: pulls the rope toward the face flaring the elbows out and squeezing the shoulder blades. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">remada_baixa</t>
@@ -1951,7 +1954,7 @@
     <t xml:space="preserve">Sentada(o) com o tronco reto, puxe o triângulo até a barriga e volte alongando as costas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a seated cable row with V-handle: upright torso, pulls the handle to the belly and returns stretching the back. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: seated cable row with V-handle: upright torso, pulls the handle to the belly and returns stretching the back. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">remada_cav</t>
@@ -1963,7 +1966,7 @@
     <t xml:space="preserve">Tronco inclinado e firme, puxe a barra em direção ao umbigo apertando as costas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a T-bar row: torso hinged and firm, pulls the bar toward the belly button squeezing the back. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree side angle, full body always in frame, steady shot, natural lighting. Exercise: landmine row machine: torso hinged forward and firm, pulls the handles toward the belly button squeezing the back. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">remada_maq</t>
@@ -1975,7 +1978,7 @@
     <t xml:space="preserve">Peito no apoio, puxe os cotovelos pra trás e segure 1 segundo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a chest-supported machine row: chest on the pad, pulls the elbows back and holds one second. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: chest-supported machine row: chest on the pad, pulls the elbows back and holds one second. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">remada_polia_uni</t>
@@ -1984,7 +1987,7 @@
     <t xml:space="preserve">Remada unilateral na polia</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a single-arm cable row: one arm at a time, elbow close to the body, no torso twisting. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: single-arm cable row: one arm at a time, elbow close to the body, no torso twisting. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">rosca_barra</t>
@@ -1996,7 +1999,7 @@
     <t xml:space="preserve">Cotovelos parados ao lado do corpo, suba a barra sem balançar o tronco.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a barbell biceps curl: elbows still at the sides, curls the bar up without swinging the torso. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: barbell biceps curl: elbows still at the sides, curls the bar up without swinging the torso. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">rosca_polia</t>
@@ -2008,7 +2011,7 @@
     <t xml:space="preserve">De frente pra polia baixa, suba a barra sem tirar os cotovelos do lugar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a cable biceps curl: facing a low cable, curls the bar up without moving the elbows. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: 45-degree front angle, full body always in frame, steady shot, natural lighting. Exercise: cable biceps curl: facing a low cable, curls the bar up without moving the elbows. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">abd_canivete</t>
@@ -2023,7 +2026,7 @@
     <t xml:space="preserve">Suba braços e pernas ao mesmo tempo tentando tocar os pés.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a V-up: lying on the back, lifts arms and legs at the same time trying to touch the feet, lowers with control. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: lying on the back, lifts the straight arms and straight legs at the same time to touch the feet above the hips, lowers with control. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">abd_infra_banco</t>
@@ -2035,7 +2038,7 @@
     <t xml:space="preserve">Segurando no banco, suba as pernas tirando o quadril do apoio e desça devagar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a lying leg raise on a bench: holding the bench behind the head, raises the legs lifting the hips off the bench, lowers slowly. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: lying leg raise on a bench: holding the bench behind the head, raises the legs lifting the hips off the bench, lowers slowly. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">abd_polia</t>
@@ -2047,7 +2050,7 @@
     <t xml:space="preserve">Ajoelhada(o), corda atrás da cabeça, enrole o tronco levando os cotovelos aos joelhos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a kneeling cable crunch: kneeling, rope behind the head, curls the torso bringing the elbows toward the knees. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: kneeling cable crunch: kneeling, rope behind the head, curls the torso bringing the elbows toward the knees. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">abd_supra</t>
@@ -2059,7 +2062,7 @@
     <t xml:space="preserve">Pés no chão, suba só até tirar as escápulas do chão, sem puxar o pescoço.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a crunch: feet on the floor, curls up just until the shoulder blades leave the floor, without pulling the neck. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: side view, full body always in frame, steady shot, natural lighting. Exercise: crunch: feet on the floor, curls up just until the shoulder blades leave the floor, without pulling the neck. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">abd_paralelas</t>
@@ -2071,7 +2074,7 @@
     <t xml:space="preserve">Apoiada(o) nos antebraços, suba os joelhos (ou as pernas estendidas) sem balançar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. The person performs 3 clean repetitions of a captain's chair knee raise: supported on the forearms on parallel bars, raises the knees without swinging. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear in a modern, well-lit gym, using the equipment described. Camera: front view, full body always in frame, steady shot, natural lighting. Exercise: supported on the forearms on a vertical knee raise station with back against the pad, raises the knees toward the chest without swinging. The person performs 3 clean, controlled repetitions. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Corrida (educativo)</t>
@@ -2095,7 +2098,7 @@
     <t xml:space="preserve">Lateral (câmera acompanhando)</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. The person performs a continuous running drill butt kicks: jogging slowly forward, kicks the heels toward the glutes, knees pointing down. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. Exercise: running drill butt kicks: jogging slowly forward, kicks the heels toward the glutes, knees pointing down. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Corrida progressiva</t>
@@ -2107,7 +2110,7 @@
     <t xml:space="preserve">Comece trotando bem devagar e vá acelerando aos poucos até um ritmo forte (não máximo) nos últimos metros. Volte andando. Pra quê: Prepara o coração e as pernas pra correr mais rápido sem susto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. The person performs a continuous progressive acceleration run: starts with an easy jog and gradually accelerates to a strong pace, tall posture, active arms. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. Exercise: progressive acceleration run: starts with an easy jog and gradually accelerates to a strong pace, tall posture, active arms. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Joelho alto</t>
@@ -2116,7 +2119,7 @@
     <t xml:space="preserve">Avance devagar subindo um joelho de cada vez até a altura do quadril, como se marchasse correndo. Tronco reto (sem jogar pra trás) e braços ativos, cotovelo a 90°. Pra quê: Fortalece a musculatura que levanta a perna e melhora a postura na corrida.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. The person performs a continuous running drill high knees: moves forward slowly driving one knee at a time to hip height, upright torso, arms at 90 degrees. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. Exercise: running drill high knees: moves forward slowly driving one knee at a time to hip height, upright torso, arms at 90 degrees. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Joelho baixo rápido</t>
@@ -2125,7 +2128,7 @@
     <t xml:space="preserve">Corra quase sem sair do lugar, com passos curtinhos e bem rápidos. O joelho sobe só um pouco e o pé toca o chão com a ponta, logo embaixo do quadril. Braços acompanham, dobrados. Pra quê: Acostuma o pé a tocar o chão rápido e leve — menos impacto e mais eficiência na passada.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. The person performs a continuous running drill low skip: moves forward with very short, fast steps, knees rising only slightly, landing on the forefoot under the hips, bent arms. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. Exercise: running drill low skip: moves forward with very short, fast steps, knees rising only slightly, landing on the forefoot under the hips, bent arms. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Passada lateral cruzada</t>
@@ -2137,7 +2140,7 @@
     <t xml:space="preserve">De lado pro caminho, ande de lado cruzando a perna de trás pela frente e depois por trás da outra, girando o quadril. Comece devagar e acelere quando pegar o ritmo. Pra quê: Solta o quadril e melhora a coordenação e o equilíbrio.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. The person performs a continuous carioca drill: moving sideways, crosses the trailing leg in front of and then behind the lead leg, hips rotating. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. Exercise: sideways crossover running drill: moving sideways, crosses the trailing leg in front of and then behind the lead leg, hips rotating, shoulders facing forward. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Passadinha de tornozelo</t>
@@ -2146,7 +2149,7 @@
     <t xml:space="preserve">Pernas quase esticadas, dê passos bem pequenos rolando o pé: toca o chão com a ponta, desce o calcanhar e empurra de novo com a ponta. Pouco avanço, muitos toques. Pra quê: Desperta tornozelo e panturrilha e ensina a pisar embaixo do corpo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. The person performs a continuous running drill ankling: legs almost straight, tiny steps rolling the foot from toes to heel and pushing off again, many contacts, little travel. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. Exercise: running drill ankling: legs almost straight, tiny steps rolling the foot from toes to heel and pushing off again, many contacts, little travel. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Perna esticada à frente</t>
@@ -2155,7 +2158,7 @@
     <t xml:space="preserve">Com as pernas quase retas, avance 'chutando' de leve à frente e puxando o pé de volta pro chão, embaixo do quadril. Tronco alto. Pra quê: Ativa o glúteo e a parte de trás da coxa, que puxam o corpo pra frente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. The person performs a continuous running drill straight-leg bounds: legs almost straight, swings each leg forward lightly and pulls the foot back down under the hips, tall torso. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. Exercise: running drill straight-leg bounds: legs almost straight, swings each leg forward lightly and pulls the foot back down under the hips, tall torso. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Saltitos alternados</t>
@@ -2164,7 +2167,7 @@
     <t xml:space="preserve">Como pular corda andando: um pulinho com a perna direita enquanto o joelho esquerdo sobe, depois troca. Braço contrário ao joelho, ritmo leve. Pra quê: Dá impulso e elasticidade pra passada, com coordenação de braço e perna.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. The person performs a continuous running drill A-skips: skipping forward, a small hop on one leg while the opposite knee drives up, opposite arm swing. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
+    <t xml:space="preserve">Vertical 9:16 fitness demonstration video, 8 seconds. A fit adult in plain dark sportswear on an outdoor running track. Camera: side view, camera tracking alongside, full body always in frame, steady shot, natural lighting. Exercise: running drill A-skips: skipping forward, a small hop on one leg while the opposite knee drives up, opposite arm swing. The person performs it continuously for the whole clip. Smooth, realistic human motion with correct exercise technique. No text, no logos, no music.</t>
   </si>
   <si>
     <t xml:space="preserve">Total de vídeos</t>
@@ -3274,10 +3277,10 @@
         <v>8</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3288,13 +3291,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>35</v>
@@ -3306,10 +3309,10 @@
         <v>84</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>8</v>
@@ -3318,7 +3321,7 @@
         <v>24</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3329,13 +3332,13 @@
         <v>15</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>19</v>
@@ -3344,13 +3347,13 @@
         <v>28</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>8</v>
@@ -3359,7 +3362,7 @@
         <v>24</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3370,13 +3373,13 @@
         <v>15</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>19</v>
@@ -3391,7 +3394,7 @@
         <v>37</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>8</v>
@@ -3400,7 +3403,7 @@
         <v>24</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3411,28 +3414,28 @@
         <v>15</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>21</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>10</v>
@@ -3441,7 +3444,7 @@
         <v>24</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3452,13 +3455,13 @@
         <v>15</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>19</v>
@@ -3473,7 +3476,7 @@
         <v>37</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>8</v>
@@ -3482,7 +3485,7 @@
         <v>24</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3493,13 +3496,13 @@
         <v>15</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>19</v>
@@ -3514,7 +3517,7 @@
         <v>37</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>6</v>
@@ -3523,7 +3526,7 @@
         <v>24</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3534,13 +3537,13 @@
         <v>15</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>35</v>
@@ -3555,7 +3558,7 @@
         <v>37</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>8</v>
@@ -3564,7 +3567,7 @@
         <v>24</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3575,28 +3578,28 @@
         <v>15</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>8</v>
@@ -3605,7 +3608,7 @@
         <v>24</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3616,13 +3619,13 @@
         <v>15</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>35</v>
@@ -3637,7 +3640,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>10</v>
@@ -3646,7 +3649,7 @@
         <v>24</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3657,13 +3660,13 @@
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>35</v>
@@ -3672,13 +3675,13 @@
         <v>28</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>8</v>
@@ -3687,7 +3690,7 @@
         <v>24</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3698,13 +3701,13 @@
         <v>15</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>19</v>
@@ -3716,10 +3719,10 @@
         <v>43</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>10</v>
@@ -3728,7 +3731,7 @@
         <v>45</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3739,13 +3742,13 @@
         <v>15</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>19</v>
@@ -3760,7 +3763,7 @@
         <v>37</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>8</v>
@@ -3769,7 +3772,7 @@
         <v>45</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3780,28 +3783,28 @@
         <v>15</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>10</v>
@@ -3810,7 +3813,7 @@
         <v>45</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3821,28 +3824,28 @@
         <v>15</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>8</v>
@@ -3851,7 +3854,7 @@
         <v>45</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3862,13 +3865,13 @@
         <v>15</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>19</v>
@@ -3877,13 +3880,13 @@
         <v>28</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>6</v>
@@ -3892,7 +3895,7 @@
         <v>45</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3903,13 +3906,13 @@
         <v>15</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>19</v>
@@ -3918,13 +3921,13 @@
         <v>28</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>8</v>
@@ -3933,7 +3936,7 @@
         <v>45</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3944,13 +3947,13 @@
         <v>15</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>19</v>
@@ -3965,7 +3968,7 @@
         <v>37</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>8</v>
@@ -3974,7 +3977,7 @@
         <v>45</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3985,19 +3988,19 @@
         <v>15</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>43</v>
@@ -4006,7 +4009,7 @@
         <v>37</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>8</v>
@@ -4015,7 +4018,7 @@
         <v>24</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4026,28 +4029,28 @@
         <v>15</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>10</v>
@@ -4056,7 +4059,7 @@
         <v>24</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4067,28 +4070,28 @@
         <v>15</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>21</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>8</v>
@@ -4097,7 +4100,7 @@
         <v>39</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4108,13 +4111,13 @@
         <v>15</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>19</v>
@@ -4126,10 +4129,10 @@
         <v>36</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>8</v>
@@ -4138,7 +4141,7 @@
         <v>39</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4149,28 +4152,28 @@
         <v>15</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>8</v>
@@ -4179,7 +4182,7 @@
         <v>39</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4190,28 +4193,28 @@
         <v>15</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>8</v>
@@ -4220,7 +4223,7 @@
         <v>65</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4231,13 +4234,13 @@
         <v>15</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>19</v>
@@ -4246,13 +4249,13 @@
         <v>28</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>8</v>
@@ -4261,7 +4264,7 @@
         <v>24</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4272,13 +4275,13 @@
         <v>15</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>35</v>
@@ -4287,13 +4290,13 @@
         <v>28</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>10</v>
@@ -4302,7 +4305,7 @@
         <v>24</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4313,13 +4316,13 @@
         <v>15</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>19</v>
@@ -4334,7 +4337,7 @@
         <v>37</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>8</v>
@@ -4343,7 +4346,7 @@
         <v>24</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4354,13 +4357,13 @@
         <v>15</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>35</v>
@@ -4369,13 +4372,13 @@
         <v>28</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K44" s="4" t="n">
         <v>8</v>
@@ -4384,7 +4387,7 @@
         <v>24</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4395,13 +4398,13 @@
         <v>15</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>19</v>
@@ -4416,7 +4419,7 @@
         <v>37</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>8</v>
@@ -4425,7 +4428,7 @@
         <v>24</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4436,28 +4439,28 @@
         <v>15</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>8</v>
@@ -4466,7 +4469,7 @@
         <v>24</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4477,13 +4480,13 @@
         <v>15</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>35</v>
@@ -4492,13 +4495,13 @@
         <v>20</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>10</v>
@@ -4507,7 +4510,7 @@
         <v>24</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4518,13 +4521,13 @@
         <v>15</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>19</v>
@@ -4536,10 +4539,10 @@
         <v>21</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>8</v>
@@ -4548,7 +4551,7 @@
         <v>39</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4559,13 +4562,13 @@
         <v>15</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>19</v>
@@ -4574,13 +4577,13 @@
         <v>28</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>10</v>
@@ -4589,7 +4592,7 @@
         <v>24</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4600,13 +4603,13 @@
         <v>15</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>35</v>
@@ -4621,7 +4624,7 @@
         <v>69</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>8</v>
@@ -4630,7 +4633,7 @@
         <v>45</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4641,28 +4644,28 @@
         <v>15</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>8</v>
@@ -4671,7 +4674,7 @@
         <v>24</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4682,28 +4685,28 @@
         <v>15</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>21</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>8</v>
@@ -4712,7 +4715,7 @@
         <v>24</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4723,28 +4726,28 @@
         <v>15</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K53" s="4" t="n">
         <v>8</v>
@@ -4753,7 +4756,7 @@
         <v>45</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4764,13 +4767,13 @@
         <v>15</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>35</v>
@@ -4779,13 +4782,13 @@
         <v>20</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>10</v>
@@ -4794,7 +4797,7 @@
         <v>45</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4805,28 +4808,28 @@
         <v>15</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>10</v>
@@ -4835,7 +4838,7 @@
         <v>45</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4846,13 +4849,13 @@
         <v>15</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>19</v>
@@ -4861,13 +4864,13 @@
         <v>20</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>69</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>8</v>
@@ -4876,7 +4879,7 @@
         <v>45</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4887,28 +4890,28 @@
         <v>15</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>8</v>
@@ -4917,7 +4920,7 @@
         <v>24</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4928,28 +4931,28 @@
         <v>15</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>8</v>
@@ -4958,7 +4961,7 @@
         <v>39</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4969,28 +4972,28 @@
         <v>15</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>21</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>8</v>
@@ -4999,7 +5002,7 @@
         <v>39</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5010,28 +5013,28 @@
         <v>15</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>8</v>
@@ -5040,7 +5043,7 @@
         <v>39</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5051,13 +5054,13 @@
         <v>15</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>19</v>
@@ -5072,7 +5075,7 @@
         <v>37</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>8</v>
@@ -5081,7 +5084,7 @@
         <v>24</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5092,13 +5095,13 @@
         <v>15</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>19</v>
@@ -5107,13 +5110,13 @@
         <v>28</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>6</v>
@@ -5122,7 +5125,7 @@
         <v>24</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5133,13 +5136,13 @@
         <v>15</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>19</v>
@@ -5148,13 +5151,13 @@
         <v>28</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>8</v>
@@ -5163,7 +5166,7 @@
         <v>65</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5174,13 +5177,13 @@
         <v>15</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>19</v>
@@ -5189,13 +5192,13 @@
         <v>28</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>8</v>
@@ -5204,7 +5207,7 @@
         <v>24</v>
       </c>
       <c r="M64" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5215,28 +5218,28 @@
         <v>15</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>8</v>
@@ -5245,7 +5248,7 @@
         <v>39</v>
       </c>
       <c r="M65" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5256,13 +5259,13 @@
         <v>15</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>19</v>
@@ -5271,13 +5274,13 @@
         <v>28</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>6</v>
@@ -5286,7 +5289,7 @@
         <v>24</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5297,13 +5300,13 @@
         <v>15</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>19</v>
@@ -5312,13 +5315,13 @@
         <v>28</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>8</v>
@@ -5327,7 +5330,7 @@
         <v>24</v>
       </c>
       <c r="M67" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5338,28 +5341,28 @@
         <v>15</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>10</v>
@@ -5368,7 +5371,7 @@
         <v>65</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5379,13 +5382,13 @@
         <v>15</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>19</v>
@@ -5394,13 +5397,13 @@
         <v>28</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>8</v>
@@ -5409,7 +5412,7 @@
         <v>65</v>
       </c>
       <c r="M69" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5420,13 +5423,13 @@
         <v>15</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>19</v>
@@ -5435,13 +5438,13 @@
         <v>28</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>8</v>
@@ -5450,7 +5453,7 @@
         <v>24</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5461,13 +5464,13 @@
         <v>15</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>19</v>
@@ -5482,7 +5485,7 @@
         <v>37</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K71" s="4" t="n">
         <v>6</v>
@@ -5491,7 +5494,7 @@
         <v>24</v>
       </c>
       <c r="M71" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5502,13 +5505,13 @@
         <v>15</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>19</v>
@@ -5517,13 +5520,13 @@
         <v>28</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I72" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K72" s="4" t="n">
         <v>10</v>
@@ -5532,7 +5535,7 @@
         <v>45</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5543,13 +5546,13 @@
         <v>15</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>35</v>
@@ -5564,16 +5567,16 @@
         <v>37</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>24</v>
       </c>
       <c r="M73" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5584,13 +5587,13 @@
         <v>15</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>19</v>
@@ -5605,16 +5608,16 @@
         <v>37</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>24</v>
       </c>
       <c r="M74" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5625,13 +5628,13 @@
         <v>15</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>19</v>
@@ -5640,13 +5643,13 @@
         <v>28</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K75" s="4" t="n">
         <v>6</v>
@@ -5655,7 +5658,7 @@
         <v>65</v>
       </c>
       <c r="M75" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5666,13 +5669,13 @@
         <v>15</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>35</v>
@@ -5681,13 +5684,13 @@
         <v>28</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K76" s="4" t="n">
         <v>8</v>
@@ -5696,7 +5699,7 @@
         <v>65</v>
       </c>
       <c r="M76" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5707,13 +5710,13 @@
         <v>15</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>19</v>
@@ -5722,13 +5725,13 @@
         <v>28</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K77" s="4" t="n">
         <v>10</v>
@@ -5737,7 +5740,7 @@
         <v>65</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5748,13 +5751,13 @@
         <v>15</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>35</v>
@@ -5766,10 +5769,10 @@
         <v>36</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K78" s="4" t="n">
         <v>8</v>
@@ -5778,7 +5781,7 @@
         <v>39</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5789,13 +5792,13 @@
         <v>15</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>35</v>
@@ -5807,10 +5810,10 @@
         <v>36</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K79" s="4" t="n">
         <v>10</v>
@@ -5819,7 +5822,7 @@
         <v>39</v>
       </c>
       <c r="M79" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5830,13 +5833,13 @@
         <v>15</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>35</v>
@@ -5845,13 +5848,13 @@
         <v>28</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K80" s="4" t="n">
         <v>10</v>
@@ -5860,7 +5863,7 @@
         <v>39</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5871,28 +5874,28 @@
         <v>15</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>10</v>
@@ -5901,7 +5904,7 @@
         <v>39</v>
       </c>
       <c r="M81" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5912,13 +5915,13 @@
         <v>15</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>19</v>
@@ -5933,7 +5936,7 @@
         <v>37</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K82" s="4" t="n">
         <v>8</v>
@@ -5942,7 +5945,7 @@
         <v>45</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5953,13 +5956,13 @@
         <v>15</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>35</v>
@@ -5974,7 +5977,7 @@
         <v>37</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K83" s="4" t="n">
         <v>8</v>
@@ -5983,7 +5986,7 @@
         <v>45</v>
       </c>
       <c r="M83" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5994,13 +5997,13 @@
         <v>15</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>19</v>
@@ -6009,13 +6012,13 @@
         <v>28</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I84" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K84" s="4" t="n">
         <v>8</v>
@@ -6024,7 +6027,7 @@
         <v>39</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6035,13 +6038,13 @@
         <v>15</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>19</v>
@@ -6050,13 +6053,13 @@
         <v>28</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I85" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K85" s="4" t="n">
         <v>8</v>
@@ -6065,7 +6068,7 @@
         <v>65</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6076,13 +6079,13 @@
         <v>15</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>19</v>
@@ -6097,7 +6100,7 @@
         <v>37</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K86" s="4" t="n">
         <v>8</v>
@@ -6106,7 +6109,7 @@
         <v>65</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6117,13 +6120,13 @@
         <v>15</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>19</v>
@@ -6132,13 +6135,13 @@
         <v>28</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K87" s="4" t="n">
         <v>8</v>
@@ -6147,7 +6150,7 @@
         <v>39</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6158,13 +6161,13 @@
         <v>15</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>35</v>
@@ -6173,13 +6176,13 @@
         <v>28</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I88" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>8</v>
@@ -6188,7 +6191,7 @@
         <v>65</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6199,28 +6202,28 @@
         <v>15</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I89" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K89" s="4" t="n">
         <v>8</v>
@@ -6229,7 +6232,7 @@
         <v>24</v>
       </c>
       <c r="M89" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6240,13 +6243,13 @@
         <v>15</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>35</v>
@@ -6255,13 +6258,13 @@
         <v>28</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I90" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>8</v>
@@ -6270,7 +6273,7 @@
         <v>65</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6281,13 +6284,13 @@
         <v>15</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>19</v>
@@ -6296,13 +6299,13 @@
         <v>28</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I91" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K91" s="4" t="n">
         <v>8</v>
@@ -6311,7 +6314,7 @@
         <v>65</v>
       </c>
       <c r="M91" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6319,13 +6322,13 @@
         <v>88</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>18</v>
@@ -6334,16 +6337,16 @@
         <v>35</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>8</v>
@@ -6352,7 +6355,7 @@
         <v>24</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6360,13 +6363,13 @@
         <v>89</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>18</v>
@@ -6375,16 +6378,16 @@
         <v>19</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K93" s="4" t="n">
         <v>8</v>
@@ -6393,7 +6396,7 @@
         <v>24</v>
       </c>
       <c r="M93" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6401,13 +6404,13 @@
         <v>90</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>18</v>
@@ -6416,16 +6419,16 @@
         <v>19</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K94" s="4" t="n">
         <v>8</v>
@@ -6434,7 +6437,7 @@
         <v>24</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6442,13 +6445,13 @@
         <v>91</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>18</v>
@@ -6457,16 +6460,16 @@
         <v>19</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K95" s="4" t="n">
         <v>8</v>
@@ -6475,7 +6478,7 @@
         <v>24</v>
       </c>
       <c r="M95" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6483,13 +6486,13 @@
         <v>92</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>18</v>
@@ -6498,16 +6501,16 @@
         <v>19</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K96" s="4" t="n">
         <v>8</v>
@@ -6516,7 +6519,7 @@
         <v>24</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6524,13 +6527,13 @@
         <v>93</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>18</v>
@@ -6539,16 +6542,16 @@
         <v>19</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K97" s="4" t="n">
         <v>8</v>
@@ -6557,7 +6560,7 @@
         <v>24</v>
       </c>
       <c r="M97" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6565,13 +6568,13 @@
         <v>94</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>18</v>
@@ -6580,16 +6583,16 @@
         <v>35</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K98" s="4" t="n">
         <v>8</v>
@@ -6598,7 +6601,7 @@
         <v>24</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6606,13 +6609,13 @@
         <v>95</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>18</v>
@@ -6621,16 +6624,16 @@
         <v>19</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>84</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K99" s="4" t="n">
         <v>8</v>
@@ -6639,7 +6642,7 @@
         <v>39</v>
       </c>
       <c r="M99" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6647,13 +6650,13 @@
         <v>96</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>18</v>
@@ -6662,16 +6665,16 @@
         <v>19</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>8</v>
@@ -6680,7 +6683,7 @@
         <v>24</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6688,31 +6691,31 @@
         <v>97</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H101" s="5" t="s">
         <v>84</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K101" s="4" t="n">
         <v>8</v>
@@ -6721,7 +6724,7 @@
         <v>65</v>
       </c>
       <c r="M101" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6729,31 +6732,31 @@
         <v>98</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>8</v>
@@ -6762,7 +6765,7 @@
         <v>24</v>
       </c>
       <c r="M102" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6770,31 +6773,31 @@
         <v>99</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K103" s="4" t="n">
         <v>8</v>
@@ -6803,7 +6806,7 @@
         <v>24</v>
       </c>
       <c r="M103" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6811,31 +6814,31 @@
         <v>100</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K104" s="4" t="n">
         <v>8</v>
@@ -6844,7 +6847,7 @@
         <v>24</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6852,31 +6855,31 @@
         <v>101</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K105" s="4" t="n">
         <v>8</v>
@@ -6885,7 +6888,7 @@
         <v>24</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6893,31 +6896,31 @@
         <v>102</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>8</v>
@@ -6926,7 +6929,7 @@
         <v>24</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6934,31 +6937,31 @@
         <v>103</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K107" s="4" t="n">
         <v>8</v>
@@ -6967,7 +6970,7 @@
         <v>24</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6975,31 +6978,31 @@
         <v>104</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K108" s="4" t="n">
         <v>8</v>
@@ -7008,7 +7011,7 @@
         <v>24</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7016,31 +7019,31 @@
         <v>105</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K109" s="4" t="n">
         <v>8</v>
@@ -7049,7 +7052,7 @@
         <v>24</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7057,31 +7060,31 @@
         <v>106</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>8</v>
@@ -7090,7 +7093,7 @@
         <v>24</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7098,31 +7101,31 @@
         <v>107</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K111" s="4" t="n">
         <v>8</v>
@@ -7131,7 +7134,7 @@
         <v>24</v>
       </c>
       <c r="M111" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7139,31 +7142,31 @@
         <v>108</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K112" s="4" t="n">
         <v>8</v>
@@ -7172,7 +7175,7 @@
         <v>45</v>
       </c>
       <c r="M112" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7180,31 +7183,31 @@
         <v>109</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K113" s="4" t="n">
         <v>8</v>
@@ -7213,7 +7216,7 @@
         <v>45</v>
       </c>
       <c r="M113" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7221,31 +7224,31 @@
         <v>110</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>8</v>
@@ -7254,7 +7257,7 @@
         <v>65</v>
       </c>
       <c r="M114" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7262,31 +7265,31 @@
         <v>111</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J115" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="K115" s="4" t="n">
         <v>8</v>
@@ -7295,7 +7298,7 @@
         <v>39</v>
       </c>
       <c r="M115" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7303,31 +7306,31 @@
         <v>112</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J116" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>8</v>
@@ -7336,7 +7339,7 @@
         <v>65</v>
       </c>
       <c r="M116" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7344,31 +7347,31 @@
         <v>113</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J117" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K117" s="4" t="n">
         <v>8</v>
@@ -7377,7 +7380,7 @@
         <v>24</v>
       </c>
       <c r="M117" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7385,31 +7388,31 @@
         <v>114</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J118" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K118" s="4" t="n">
         <v>8</v>
@@ -7418,7 +7421,7 @@
         <v>24</v>
       </c>
       <c r="M118" s="5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7426,31 +7429,31 @@
         <v>115</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J119" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K119" s="4" t="n">
         <v>8</v>
@@ -7459,7 +7462,7 @@
         <v>24</v>
       </c>
       <c r="M119" s="5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7467,31 +7470,31 @@
         <v>116</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K120" s="4" t="n">
         <v>8</v>
@@ -7500,7 +7503,7 @@
         <v>39</v>
       </c>
       <c r="M120" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7508,31 +7511,31 @@
         <v>117</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J121" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K121" s="4" t="n">
         <v>8</v>
@@ -7541,7 +7544,7 @@
         <v>24</v>
       </c>
       <c r="M121" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7549,31 +7552,31 @@
         <v>118</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="K122" s="4" t="n">
         <v>8</v>
@@ -7582,7 +7585,7 @@
         <v>24</v>
       </c>
       <c r="M122" s="5" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7590,31 +7593,31 @@
         <v>119</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J123" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K123" s="4" t="n">
         <v>8</v>
@@ -7623,7 +7626,7 @@
         <v>39</v>
       </c>
       <c r="M123" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7631,31 +7634,31 @@
         <v>120</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J124" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K124" s="4" t="n">
         <v>8</v>
@@ -7664,7 +7667,7 @@
         <v>39</v>
       </c>
       <c r="M124" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7672,31 +7675,31 @@
         <v>121</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J125" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K125" s="4" t="n">
         <v>8</v>
@@ -7705,7 +7708,7 @@
         <v>39</v>
       </c>
       <c r="M125" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7713,31 +7716,31 @@
         <v>122</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J126" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>8</v>
@@ -7746,7 +7749,7 @@
         <v>65</v>
       </c>
       <c r="M126" s="5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7754,31 +7757,31 @@
         <v>123</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J127" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K127" s="4" t="n">
         <v>8</v>
@@ -7787,7 +7790,7 @@
         <v>24</v>
       </c>
       <c r="M127" s="5" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7795,31 +7798,31 @@
         <v>124</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J128" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K128" s="4" t="n">
         <v>8</v>
@@ -7828,7 +7831,7 @@
         <v>39</v>
       </c>
       <c r="M128" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7836,31 +7839,31 @@
         <v>125</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J129" s="5" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="K129" s="4" t="n">
         <v>8</v>
@@ -7869,7 +7872,7 @@
         <v>65</v>
       </c>
       <c r="M129" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7877,31 +7880,31 @@
         <v>126</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>8</v>
@@ -7910,7 +7913,7 @@
         <v>65</v>
       </c>
       <c r="M130" s="5" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7918,31 +7921,31 @@
         <v>127</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J131" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="K131" s="4" t="n">
         <v>8</v>
@@ -7951,7 +7954,7 @@
         <v>65</v>
       </c>
       <c r="M131" s="5" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7959,31 +7962,31 @@
         <v>128</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J132" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K132" s="4" t="n">
         <v>8</v>
@@ -7992,7 +7995,7 @@
         <v>39</v>
       </c>
       <c r="M132" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8000,31 +8003,31 @@
         <v>129</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I133" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J133" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K133" s="4" t="n">
         <v>8</v>
@@ -8033,7 +8036,7 @@
         <v>24</v>
       </c>
       <c r="M133" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8041,31 +8044,31 @@
         <v>130</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J134" s="5" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K134" s="4" t="n">
         <v>8</v>
@@ -8074,7 +8077,7 @@
         <v>45</v>
       </c>
       <c r="M134" s="5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8082,31 +8085,31 @@
         <v>131</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J135" s="5" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="K135" s="4" t="n">
         <v>8</v>
@@ -8115,7 +8118,7 @@
         <v>24</v>
       </c>
       <c r="M135" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8123,31 +8126,31 @@
         <v>132</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I136" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J136" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K136" s="4" t="n">
         <v>8</v>
@@ -8156,7 +8159,7 @@
         <v>24</v>
       </c>
       <c r="M136" s="5" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8164,31 +8167,31 @@
         <v>133</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I137" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J137" s="5" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K137" s="4" t="n">
         <v>8</v>
@@ -8197,7 +8200,7 @@
         <v>39</v>
       </c>
       <c r="M137" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8205,31 +8208,31 @@
         <v>134</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J138" s="5" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="K138" s="4" t="n">
         <v>8</v>
@@ -8238,7 +8241,7 @@
         <v>39</v>
       </c>
       <c r="M138" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8246,31 +8249,31 @@
         <v>135</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H139" s="5" t="s">
         <v>84</v>
       </c>
       <c r="I139" s="5" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J139" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K139" s="4" t="n">
         <v>8</v>
@@ -8279,7 +8282,7 @@
         <v>24</v>
       </c>
       <c r="M139" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8287,31 +8290,31 @@
         <v>136</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H140" s="5" t="s">
         <v>84</v>
       </c>
       <c r="I140" s="5" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J140" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="K140" s="4" t="n">
         <v>8</v>
@@ -8320,7 +8323,7 @@
         <v>24</v>
       </c>
       <c r="M140" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8328,31 +8331,31 @@
         <v>137</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H141" s="5" t="s">
         <v>84</v>
       </c>
       <c r="I141" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J141" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K141" s="4" t="n">
         <v>8</v>
@@ -8361,7 +8364,7 @@
         <v>24</v>
       </c>
       <c r="M141" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8369,31 +8372,31 @@
         <v>138</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I142" s="5" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J142" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="K142" s="4" t="n">
         <v>8</v>
@@ -8402,7 +8405,7 @@
         <v>24</v>
       </c>
       <c r="M142" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8410,31 +8413,31 @@
         <v>139</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J143" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="K143" s="4" t="n">
         <v>8</v>
@@ -8443,7 +8446,7 @@
         <v>65</v>
       </c>
       <c r="M143" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8451,16 +8454,16 @@
         <v>140</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>19</v>
@@ -8469,22 +8472,22 @@
         <v>28</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I144" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J144" s="5" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K144" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L144" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M144" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8492,16 +8495,16 @@
         <v>141</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>19</v>
@@ -8510,22 +8513,22 @@
         <v>28</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I145" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J145" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="K145" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L145" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M145" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8533,16 +8536,16 @@
         <v>142</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>19</v>
@@ -8551,22 +8554,22 @@
         <v>28</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I146" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J146" s="5" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="K146" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L146" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M146" s="5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8574,16 +8577,16 @@
         <v>143</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>19</v>
@@ -8592,22 +8595,22 @@
         <v>28</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I147" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J147" s="5" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="K147" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L147" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M147" s="5" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8615,16 +8618,16 @@
         <v>144</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>19</v>
@@ -8633,22 +8636,22 @@
         <v>28</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J148" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="K148" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L148" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M148" s="5" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8656,16 +8659,16 @@
         <v>145</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>19</v>
@@ -8674,22 +8677,22 @@
         <v>28</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I149" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J149" s="5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="K149" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L149" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M149" s="5" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8697,16 +8700,16 @@
         <v>146</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>19</v>
@@ -8715,22 +8718,22 @@
         <v>28</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I150" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J150" s="5" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="K150" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L150" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M150" s="5" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8738,16 +8741,16 @@
         <v>147</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>19</v>
@@ -8756,27 +8759,27 @@
         <v>28</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I151" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J151" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K151" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L151" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M151" s="5" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J153" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="K153" s="8" t="n">
         <f aca="false">COUNTA(D5:D151)</f>
@@ -8785,7 +8788,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J154" s="7" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="K154" s="8" t="n">
         <f aca="false">COUNTIF(B5:B151,"Casa")</f>
@@ -8794,7 +8797,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J155" s="7" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="K155" s="8" t="n">
         <f aca="false">COUNTIF(B5:B151,"Academia")</f>
@@ -8803,7 +8806,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J156" s="7" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="K156" s="8" t="n">
         <f aca="false">COUNTIF(B5:B151,"Corrida*")</f>
@@ -8812,20 +8815,20 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J157" s="7" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="K157" s="9" t="n">
         <f aca="false">SUM(K5:K151)</f>
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J158" s="7" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="K158" s="10" t="n">
         <f aca="false">K157/60</f>
-        <v>19.8666666666667</v>
+        <v>19.9333333333333</v>
       </c>
     </row>
   </sheetData>
